--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T11:05:22+00:00</t>
+    <t>2024-02-01T12:40:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T12:40:33+00:00</t>
+    <t>2024-02-01T12:41:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T12:41:44+00:00</t>
+    <t>2024-02-01T12:52:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T12:52:14+00:00</t>
+    <t>2024-02-01T13:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:00:09+00:00</t>
+    <t>2024-02-01T13:47:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:47:57+00:00</t>
+    <t>2024-02-01T13:51:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:51:16+00:00</t>
+    <t>2024-02-01T13:53:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:53:33+00:00</t>
+    <t>2024-02-01T13:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:54:03+00:00</t>
+    <t>2024-02-01T13:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:57:52+00:00</t>
+    <t>2024-02-01T14:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/ig/nr-maj-schema/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:01:03+00:00</t>
+    <t>2024-02-01T14:12:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
